--- a/sepreim/config.xlsx
+++ b/sepreim/config.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30023"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30110"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\COPREIM\SEPREIM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="37" documentId="13_ncr:1_{FBC06D43-FC39-47E4-9407-81C46EA59553}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F6084BB-0812-49E2-9A47-9328567D2395}"/>
+  <xr:revisionPtr revIDLastSave="166" documentId="13_ncr:1_{FBC06D43-FC39-47E4-9407-81C46EA59553}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{588959FD-E9B0-4648-B67D-5C192DD361CF}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="5355" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet2" sheetId="3" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="4" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="153">
   <si>
     <t>id</t>
   </si>
@@ -44,6 +44,9 @@
     <t>logo_senador</t>
   </si>
   <si>
+    <t>revisao_servso</t>
+  </si>
+  <si>
     <t>sigraf_formato</t>
   </si>
   <si>
@@ -167,6 +170,9 @@
     <t>Trabalho sem logomarca do senador</t>
   </si>
   <si>
+    <t>Trabalho já está revisado</t>
+  </si>
+  <si>
     <t>Formato correto na Ordem de Serviço</t>
   </si>
   <si>
@@ -261,6 +267,9 @@
   </si>
   <si>
     <t>details</t>
+  </si>
+  <si>
+    <t>Verficar se a revisão será feita pela SEGRAF ou já foi feita pelo cliente</t>
   </si>
   <si>
     <t>Para lombada colada, nas primeiras e últimas páginas e nas partes internas da capa a distância mínima deve ser de 10 mm</t>
@@ -447,6 +456,9 @@
     <t>Enviar e-mail Logomarca e Atividade Parlamentar</t>
   </si>
   <si>
+    <t>Enviar para SERVSO</t>
+  </si>
+  <si>
     <t>Pedir correção do formato para SEAUFAT</t>
   </si>
   <si>
@@ -478,6 +490,9 @@
   </si>
   <si>
     <t>impressao, plotagem, expediente</t>
+  </si>
+  <si>
+    <t>impressao, plotagem</t>
   </si>
   <si>
     <t>impressao, expediente</t>
@@ -490,20 +505,124 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="4" tint="-0.499984740745262"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="6" tint="-0.249977111117893"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="5" tint="-0.249977111117893"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="7" tint="-0.249977111117893"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -518,10 +637,55 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -737,1028 +901,1052 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3236D795-EBC6-4499-9CA9-63D29694CD4F}">
-  <dimension ref="A1:AG10"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC9DC384-A7A3-4CB6-B76F-D3A8F330DE38}">
+  <dimension ref="A1:AH10"/>
+  <sheetFormatPr defaultColWidth="59" defaultRowHeight="30" customHeight="1"/>
   <cols>
-    <col min="2" max="2" width="36.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="34.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="36.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="27.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="28" width="36.5703125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="33" bestFit="1" customWidth="1"/>
-    <col min="30" max="33" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.42578125" style="12" customWidth="1"/>
+    <col min="2" max="16384" width="59" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33">
-      <c r="A1" t="s">
+    <row r="1" spans="1:34" s="6" customFormat="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Z1" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AA1" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AB1" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AC1" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AD1" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AE1" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AF1" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AG1" s="5" t="s">
         <v>32</v>
       </c>
+      <c r="AH1" s="5" t="s">
+        <v>33</v>
+      </c>
     </row>
-    <row r="2" spans="1:33">
-      <c r="A2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B2" s="1" t="s">
+    <row r="2" spans="1:34" ht="30" customHeight="1">
+      <c r="A2" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B2" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="D2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="C2" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="G2" t="s">
+      <c r="D2" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="E2" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="F2" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="L2" s="1" t="s">
+      <c r="G2" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="H2" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="I2" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="J2" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="K2" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="L2" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="R2" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="Y2" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="Z2" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AA2" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AB2" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>37</v>
-      </c>
-      <c r="AD2" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AE2" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AF2" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AG2" s="1" t="s">
-        <v>37</v>
+      <c r="M2" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="N2" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="O2" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="P2" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q2" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="R2" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="S2" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="T2" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="U2" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="V2" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="W2" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="X2" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y2" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z2" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="AA2" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB2" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC2" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD2" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="AE2" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="AF2" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG2" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="AH2" s="16" t="s">
+        <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:33">
-      <c r="A3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="1" t="s">
+    <row r="3" spans="1:34" ht="30" customHeight="1">
+      <c r="A3" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G3" t="s">
-        <v>39</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="T3" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="U3" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="V3" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="W3" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="X3" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y3" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="Z3" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AA3" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB3" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AD3" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AE3" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AF3" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AG3" s="1" t="s">
-        <v>39</v>
+      <c r="B3" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="M3" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="N3" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="O3" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="P3" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q3" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="R3" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="S3" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="T3" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="U3" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="V3" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="W3" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="X3" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y3" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z3" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA3" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB3" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="AC3" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="AD3" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="AE3" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="AF3" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="AG3" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH3" s="10" t="s">
+        <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:33" ht="24">
-      <c r="A4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4" s="1" t="s">
+    <row r="4" spans="1:34" ht="91.5" customHeight="1">
+      <c r="A4" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C4" t="s">
+      <c r="B4" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D4" t="s">
+      <c r="C4" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="D4" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="F4" t="s">
+      <c r="E4" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="G4" t="s">
+      <c r="F4" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="G4" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="H4" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="I4" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="J4" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="K4" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="M4" s="1" t="s">
+      <c r="L4" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="N4" s="1" t="s">
+      <c r="M4" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="O4" s="1" t="s">
+      <c r="N4" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="P4" s="1" t="s">
+      <c r="O4" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="Q4" s="1" t="s">
+      <c r="P4" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="R4" s="1" t="s">
+      <c r="Q4" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="S4" s="1" t="s">
+      <c r="R4" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="T4" s="1" t="s">
+      <c r="S4" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="U4" s="1" t="s">
+      <c r="T4" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="V4" s="1" t="s">
+      <c r="U4" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="W4" s="1" t="s">
+      <c r="V4" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="X4" s="1" t="s">
+      <c r="W4" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="Y4" s="1" t="s">
+      <c r="X4" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="Z4" s="1" t="s">
+      <c r="Y4" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="AA4" s="1" t="s">
+      <c r="Z4" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="AB4" s="1" t="s">
+      <c r="AA4" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="AC4" t="s">
+      <c r="AB4" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="AD4" s="1" t="s">
+      <c r="AC4" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="AE4" s="1" t="s">
+      <c r="AD4" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="AF4" s="1" t="s">
+      <c r="AE4" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="AG4" s="1" t="s">
+      <c r="AF4" s="10" t="s">
         <v>73</v>
       </c>
+      <c r="AG4" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="AH4" s="10" t="s">
+        <v>75</v>
+      </c>
     </row>
-    <row r="5" spans="1:33" ht="60">
-      <c r="A5" t="s">
-        <v>74</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D5" t="s">
-        <v>40</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F5" t="s">
-        <v>40</v>
-      </c>
-      <c r="G5" t="s">
-        <v>40</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="O5" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="P5" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q5" s="1" t="s">
+    <row r="5" spans="1:34" ht="131.25" customHeight="1">
+      <c r="A5" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="R5" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="S5" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="T5" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="U5" s="1" t="s">
+      <c r="B5" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="V5" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="W5" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="X5" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y5" s="1" t="s">
+      <c r="D5" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="M5" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="N5" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="O5" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="P5" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="Z5" s="1" t="s">
+      <c r="Q5" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="R5" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="AA5" s="1" t="s">
+      <c r="S5" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="T5" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="U5" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="V5" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="AB5" s="1" t="s">
+      <c r="W5" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="X5" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y5" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z5" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="AC5" t="s">
-        <v>40</v>
-      </c>
-      <c r="AD5" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AE5" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AF5" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AG5" s="1" t="s">
-        <v>40</v>
+      <c r="AA5" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="AB5" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="AC5" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="AD5" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE5" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF5" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG5" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH5" s="10" t="s">
+        <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:33">
-      <c r="A6" t="s">
-        <v>82</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="C6" t="s">
-        <v>83</v>
-      </c>
-      <c r="D6" t="s">
-        <v>83</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F6" t="s">
-        <v>84</v>
-      </c>
-      <c r="G6" t="s">
-        <v>84</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="O6" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="P6" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q6" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="R6" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="S6" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="T6" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="U6" s="1" t="s">
+    <row r="6" spans="1:34" ht="25.5" customHeight="1">
+      <c r="A6" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="V6" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="W6" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="X6" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="Y6" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="Z6" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="AA6" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="AB6" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="AC6" t="s">
-        <v>84</v>
-      </c>
-      <c r="AD6" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="AE6" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="AF6" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="AG6" s="1" t="s">
-        <v>83</v>
+      <c r="B6" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="K6" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="M6" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="N6" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="O6" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="P6" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q6" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="R6" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="S6" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="T6" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="U6" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="V6" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="W6" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="X6" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y6" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="Z6" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="AA6" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB6" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="AC6" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="AD6" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="AE6" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="AF6" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="AG6" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="AH6" s="10" t="s">
+        <v>86</v>
       </c>
     </row>
-    <row r="7" spans="1:33" ht="24">
-      <c r="A7" t="s">
-        <v>86</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D7" t="s">
-        <v>40</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F7" t="s">
-        <v>87</v>
-      </c>
-      <c r="G7" t="s">
-        <v>88</v>
-      </c>
-      <c r="H7" s="1" t="s">
+    <row r="7" spans="1:34" ht="91.5" customHeight="1">
+      <c r="A7" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="B7" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G7" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="H7" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="K7" s="1" t="s">
+      <c r="I7" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="L7" s="1" t="s">
+      <c r="J7" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="M7" s="1" t="s">
+      <c r="K7" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="N7" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="O7" s="1" t="s">
+      <c r="L7" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="P7" s="1" t="s">
+      <c r="M7" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="Q7" s="1" t="s">
+      <c r="N7" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="R7" s="1" t="s">
+      <c r="O7" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="P7" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="S7" s="1" t="s">
+      <c r="Q7" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="T7" s="1" t="s">
+      <c r="R7" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="U7" s="1" t="s">
+      <c r="S7" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="V7" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="W7" s="1" t="s">
+      <c r="T7" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="X7" s="1" t="s">
+      <c r="U7" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="Y7" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="Z7" s="1" t="s">
+      <c r="V7" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="AA7" s="1" t="s">
+      <c r="W7" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="X7" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="AB7" s="1" t="s">
+      <c r="Y7" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="AC7" t="s">
+      <c r="Z7" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA7" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="AD7" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AE7" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AF7" s="1" t="s">
+      <c r="AB7" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="AG7" s="1" t="s">
-        <v>40</v>
+      <c r="AC7" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="AD7" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="AE7" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF7" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG7" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="AH7" s="10" t="s">
+        <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:33" ht="72">
-      <c r="A8" t="s">
-        <v>109</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C8" t="s">
-        <v>40</v>
-      </c>
-      <c r="D8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F8" t="s">
-        <v>110</v>
-      </c>
-      <c r="G8" t="s">
-        <v>111</v>
-      </c>
-      <c r="H8" s="1" t="s">
+    <row r="8" spans="1:34" ht="91.5" customHeight="1">
+      <c r="A8" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="B8" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G8" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="J8" s="1" t="s">
+      <c r="H8" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="K8" s="1" t="s">
+      <c r="I8" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="L8" s="1" t="s">
+      <c r="J8" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="M8" s="1" t="s">
+      <c r="K8" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="N8" s="1" t="s">
+      <c r="L8" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="O8" s="1" t="s">
+      <c r="M8" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="P8" s="1" t="s">
+      <c r="N8" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="Q8" s="1" t="s">
+      <c r="O8" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="R8" s="1" t="s">
+      <c r="P8" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="S8" s="1" t="s">
+      <c r="Q8" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="T8" s="1" t="s">
+      <c r="R8" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="U8" s="1" t="s">
+      <c r="S8" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="V8" s="1" t="s">
+      <c r="T8" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="W8" s="1" t="s">
+      <c r="U8" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="X8" s="1" t="s">
+      <c r="V8" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="Y8" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="Z8" s="1" t="s">
+      <c r="W8" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="AA8" s="1" t="s">
+      <c r="X8" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="AB8" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AC8" t="s">
+      <c r="Y8" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="AD8" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AE8" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AF8" s="1" t="s">
+      <c r="Z8" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA8" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="AG8" s="1" t="s">
-        <v>40</v>
+      <c r="AB8" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="AC8" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD8" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="AE8" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF8" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG8" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="AH8" s="10" t="s">
+        <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:33" ht="24">
-      <c r="A9" t="s">
-        <v>133</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="C9" t="s">
-        <v>135</v>
-      </c>
-      <c r="D9" t="s">
+    <row r="9" spans="1:34" ht="91.5" customHeight="1">
+      <c r="A9" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="B9" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="F9" t="s">
-        <v>40</v>
-      </c>
-      <c r="G9" t="s">
-        <v>40</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="O9" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="P9" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q9" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="R9" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="S9" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="T9" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="U9" s="1" t="s">
+      <c r="C9" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="V9" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="W9" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="X9" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y9" s="1" t="s">
+      <c r="D9" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="Z9" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AA9" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB9" s="1" t="s">
+      <c r="E9" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="AC9" t="s">
-        <v>40</v>
-      </c>
-      <c r="AD9" s="1" t="s">
+      <c r="F9" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="AE9" s="1" t="s">
+      <c r="G9" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="K9" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="M9" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="N9" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="O9" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="P9" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q9" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="R9" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="S9" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="T9" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="U9" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="V9" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="AF9" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AG9" s="1" t="s">
+      <c r="W9" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="X9" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y9" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z9" s="10" t="s">
         <v>143</v>
       </c>
+      <c r="AA9" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB9" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="AC9" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="AD9" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE9" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="AF9" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="AG9" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH9" s="10" t="s">
+        <v>147</v>
+      </c>
     </row>
-    <row r="10" spans="1:33">
-      <c r="A10" t="s">
-        <v>144</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="C10" t="s">
-        <v>145</v>
-      </c>
-      <c r="D10" t="s">
-        <v>146</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="F10" t="s">
-        <v>147</v>
-      </c>
-      <c r="G10" t="s">
-        <v>146</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="O10" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="P10" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="Q10" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="R10" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="S10" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="T10" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="U10" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="V10" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="W10" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="X10" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="Y10" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="Z10" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="AA10" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="AB10" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="AC10" t="s">
-        <v>147</v>
-      </c>
-      <c r="AD10" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="AE10" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="AF10" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="AG10" s="1" t="s">
-        <v>147</v>
+    <row r="10" spans="1:34" ht="30" customHeight="1">
+      <c r="A10" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="K10" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="M10" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="N10" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="O10" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="P10" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="Q10" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="R10" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="S10" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="T10" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="U10" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="V10" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="W10" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="X10" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="Y10" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="Z10" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="AA10" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="AB10" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="AC10" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="AD10" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="AE10" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="AF10" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="AG10" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="AH10" s="10" t="s">
+        <v>152</v>
       </c>
     </row>
   </sheetData>

--- a/sepreim/config.xlsx
+++ b/sepreim/config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\COPREIM\SEPREIM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="166" documentId="13_ncr:1_{FBC06D43-FC39-47E4-9407-81C46EA59553}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{588959FD-E9B0-4648-B67D-5C192DD361CF}"/>
+  <xr:revisionPtr revIDLastSave="168" documentId="13_ncr:1_{FBC06D43-FC39-47E4-9407-81C46EA59553}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08A27821-0967-47D3-8385-4CD67C690520}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="5355" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/sepreim/config.xlsx
+++ b/sepreim/config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\COPREIM\SEPREIM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="168" documentId="13_ncr:1_{FBC06D43-FC39-47E4-9407-81C46EA59553}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08A27821-0967-47D3-8385-4CD67C690520}"/>
+  <xr:revisionPtr revIDLastSave="256" documentId="13_ncr:1_{FBC06D43-FC39-47E4-9407-81C46EA59553}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{70E29EF8-059F-4A4E-9D26-E6B6FCC30D34}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="5355" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="157">
   <si>
     <t>id</t>
   </si>
@@ -137,6 +137,9 @@
     <t>cartao_visita</t>
   </si>
   <si>
+    <t>modelo_cliche</t>
+  </si>
+  <si>
     <t>chancela_correios</t>
   </si>
   <si>
@@ -261,6 +264,9 @@
   </si>
   <si>
     <t>Cartão de visitas no padrão do Senado</t>
+  </si>
+  <si>
+    <t>Modelo de relevo/douração impresso na pasta</t>
   </si>
   <si>
     <t>Envelope com a chancela dos Correios</t>
@@ -297,6 +303,9 @@
     <t>Para espiral, a "lombada" deve ter menos de 50 mm</t>
   </si>
   <si>
+    <t>Os trabalhos com relevo ou douração precisam de um modelo impresso na pasta</t>
+  </si>
+  <si>
     <t>action</t>
   </si>
   <si>
@@ -481,6 +490,9 @@
   </si>
   <si>
     <t>Solicitar atualização do colofão para SEFPRO</t>
+  </si>
+  <si>
+    <t>Incluir um modelo impresso na pasta.</t>
   </si>
   <si>
     <t>Confirmar a chancela dos Correios com SEAUFAT</t>
@@ -513,48 +525,41 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="14"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
+      <b/>
+      <sz val="12"/>
+      <color theme="0" tint="-0.14999847407452621"/>
+      <name val="Verdana"/>
     </font>
     <font>
       <b/>
-      <sz val="14"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
+      <name val="Verdana"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
+      <sz val="12"/>
+      <color theme="4" tint="-0.499984740745262"/>
+      <name val="Verdana"/>
     </font>
     <font>
-      <sz val="14"/>
-      <color theme="4" tint="-0.499984740745262"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
+      <sz val="12"/>
+      <color theme="6" tint="-0.249977111117893"/>
+      <name val="Verdana"/>
     </font>
     <font>
-      <sz val="14"/>
-      <color theme="6" tint="-0.249977111117893"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
+      <sz val="12"/>
+      <color theme="5" tint="-0.249977111117893"/>
+      <name val="Verdana"/>
     </font>
     <font>
-      <sz val="14"/>
-      <color theme="5" tint="-0.249977111117893"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
+      <sz val="12"/>
+      <color theme="7" tint="-0.249977111117893"/>
+      <name val="Verdana"/>
     </font>
     <font>
-      <sz val="14"/>
-      <color theme="7" tint="-0.249977111117893"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Verdana"/>
     </font>
   </fonts>
   <fills count="12">
@@ -563,12 +568,6 @@
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -624,8 +623,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -633,58 +638,410 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </top>
+      <bottom style="medium">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
@@ -902,1051 +1259,1083 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC9DC384-A7A3-4CB6-B76F-D3A8F330DE38}">
-  <dimension ref="A1:AH10"/>
-  <sheetFormatPr defaultColWidth="59" defaultRowHeight="30" customHeight="1"/>
+  <dimension ref="A1:AI10"/>
+  <sheetFormatPr defaultColWidth="54.5703125" defaultRowHeight="30" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="17.42578125" style="12" customWidth="1"/>
-    <col min="2" max="16384" width="59" style="11"/>
+    <col min="1" max="1" width="15.7109375" style="3" customWidth="1"/>
+    <col min="2" max="31" width="54.5703125" style="2"/>
+    <col min="32" max="32" width="54.5703125" style="4"/>
+    <col min="33" max="16384" width="54.5703125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" s="6" customFormat="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:35" s="1" customFormat="1" ht="30" customHeight="1">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="M1" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="N1" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="O1" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="P1" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="Q1" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="R1" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="S1" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="5" t="s">
+      <c r="T1" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="5" t="s">
+      <c r="U1" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="5" t="s">
+      <c r="V1" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="5" t="s">
+      <c r="W1" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="5" t="s">
+      <c r="X1" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="5" t="s">
+      <c r="Y1" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="5" t="s">
+      <c r="Z1" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="5" t="s">
+      <c r="AA1" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="5" t="s">
+      <c r="AB1" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="5" t="s">
+      <c r="AC1" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="5" t="s">
+      <c r="AD1" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="5" t="s">
+      <c r="AE1" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="5" t="s">
+      <c r="AF1" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="5" t="s">
+      <c r="AG1" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="5" t="s">
+      <c r="AH1" s="18" t="s">
         <v>33</v>
       </c>
+      <c r="AI1" s="19" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="2" spans="1:34" ht="30" customHeight="1">
-      <c r="A2" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B2" s="13" t="s">
+    <row r="2" spans="1:35" ht="30" customHeight="1">
+      <c r="A2" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="B2" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="E2" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="F2" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="G2" s="15" t="s">
+      <c r="C2" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="D2" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="I2" s="15" t="s">
+      <c r="E2" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="J2" s="15" t="s">
+      <c r="F2" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="K2" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="L2" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="M2" s="16" t="s">
+      <c r="G2" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="N2" s="16" t="s">
+      <c r="H2" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="O2" s="16" t="s">
+      <c r="I2" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="P2" s="16" t="s">
+      <c r="J2" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="Q2" s="16" t="s">
+      <c r="K2" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="R2" s="16" t="s">
+      <c r="L2" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="S2" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="T2" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="U2" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="V2" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="W2" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="X2" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y2" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="Z2" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="AA2" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="AB2" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="AC2" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD2" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="AE2" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="AF2" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG2" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="AH2" s="16" t="s">
-        <v>38</v>
+      <c r="M2" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="N2" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="O2" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="P2" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q2" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="R2" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="S2" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="T2" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="U2" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="V2" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="W2" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="X2" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y2" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="Z2" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA2" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB2" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC2" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD2" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE2" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF2" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG2" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH2" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI2" s="29" t="s">
+        <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:34" ht="30" customHeight="1">
-      <c r="A3" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="7" t="s">
+    <row r="3" spans="1:35" ht="30" customHeight="1">
+      <c r="A3" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="K3" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="L3" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="M3" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="N3" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="O3" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="P3" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q3" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="R3" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="S3" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="T3" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="U3" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="V3" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="W3" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="X3" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y3" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="Z3" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="AA3" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB3" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="AC3" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="AD3" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="AE3" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="AF3" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="AG3" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="AH3" s="10" t="s">
-        <v>40</v>
+      <c r="B3" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="F3" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="G3" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="H3" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="I3" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="J3" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="K3" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="L3" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="M3" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="N3" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="O3" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="P3" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q3" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="R3" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="S3" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="T3" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="U3" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="V3" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="W3" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="X3" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y3" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z3" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA3" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB3" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="AC3" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD3" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE3" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF3" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG3" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH3" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="AI3" s="39" t="s">
+        <v>41</v>
       </c>
     </row>
-    <row r="4" spans="1:34" ht="91.5" customHeight="1">
-      <c r="A4" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B4" s="7" t="s">
+    <row r="4" spans="1:35" ht="122.25" customHeight="1">
+      <c r="A4" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="B4" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="C4" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="D4" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="E4" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="F4" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="G4" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="H4" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="J4" s="9" t="s">
+      <c r="I4" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="K4" s="9" t="s">
+      <c r="J4" s="32" t="s">
         <v>52</v>
       </c>
-      <c r="L4" s="9" t="s">
+      <c r="K4" s="32" t="s">
         <v>53</v>
       </c>
-      <c r="M4" s="10" t="s">
+      <c r="L4" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="N4" s="10" t="s">
+      <c r="M4" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="O4" s="10" t="s">
+      <c r="N4" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="P4" s="10" t="s">
+      <c r="O4" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="Q4" s="10" t="s">
+      <c r="P4" s="33" t="s">
         <v>58</v>
       </c>
-      <c r="R4" s="10" t="s">
+      <c r="Q4" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="S4" s="10" t="s">
+      <c r="R4" s="33" t="s">
         <v>60</v>
       </c>
-      <c r="T4" s="10" t="s">
+      <c r="S4" s="33" t="s">
         <v>61</v>
       </c>
-      <c r="U4" s="10" t="s">
+      <c r="T4" s="33" t="s">
         <v>62</v>
       </c>
-      <c r="V4" s="10" t="s">
+      <c r="U4" s="33" t="s">
         <v>63</v>
       </c>
-      <c r="W4" s="10" t="s">
+      <c r="V4" s="33" t="s">
         <v>64</v>
       </c>
-      <c r="X4" s="10" t="s">
+      <c r="W4" s="33" t="s">
         <v>65</v>
       </c>
-      <c r="Y4" s="10" t="s">
+      <c r="X4" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="Z4" s="10" t="s">
+      <c r="Y4" s="33" t="s">
         <v>67</v>
       </c>
-      <c r="AA4" s="10" t="s">
+      <c r="Z4" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="AB4" s="10" t="s">
+      <c r="AA4" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="AC4" s="10" t="s">
+      <c r="AB4" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="AD4" s="10" t="s">
+      <c r="AC4" s="33" t="s">
         <v>71</v>
       </c>
-      <c r="AE4" s="10" t="s">
+      <c r="AD4" s="33" t="s">
         <v>72</v>
       </c>
-      <c r="AF4" s="10" t="s">
+      <c r="AE4" s="33" t="s">
         <v>73</v>
       </c>
-      <c r="AG4" s="10" t="s">
+      <c r="AF4" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="AH4" s="10" t="s">
+      <c r="AG4" s="33" t="s">
         <v>75</v>
       </c>
+      <c r="AH4" s="33" t="s">
+        <v>76</v>
+      </c>
+      <c r="AI4" s="34" t="s">
+        <v>77</v>
+      </c>
     </row>
-    <row r="5" spans="1:34" ht="131.25" customHeight="1">
-      <c r="A5" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="I5" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="J5" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="K5" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="L5" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="M5" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="N5" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="O5" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="P5" s="10" t="s">
+    <row r="5" spans="1:35" ht="122.25" customHeight="1">
+      <c r="A5" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="Q5" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="R5" s="10" t="s">
+      <c r="B5" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="S5" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="T5" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="U5" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="V5" s="10" t="s">
+      <c r="D5" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="M5" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="N5" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="O5" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="P5" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="W5" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="X5" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y5" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="Z5" s="10" t="s">
+      <c r="Q5" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="R5" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="AA5" s="10" t="s">
+      <c r="S5" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="T5" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="U5" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="V5" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="AB5" s="10" t="s">
+      <c r="W5" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="X5" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y5" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z5" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="AC5" s="10" t="s">
+      <c r="AA5" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="AD5" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="AE5" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="AF5" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG5" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH5" s="10" t="s">
-        <v>41</v>
+      <c r="AB5" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC5" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="AD5" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE5" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF5" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="AG5" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH5" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="AI5" s="9" t="s">
+        <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:34" ht="25.5" customHeight="1">
-      <c r="A6" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="I6" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="J6" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K6" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="L6" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="M6" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="N6" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="O6" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="P6" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q6" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="R6" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="S6" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="T6" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="U6" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="V6" s="10" t="s">
+    <row r="6" spans="1:35" ht="30.75" customHeight="1">
+      <c r="A6" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="W6" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="X6" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="Y6" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="Z6" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="AA6" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="AB6" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="AC6" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="AD6" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="AE6" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="AF6" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="AG6" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="AH6" s="10" t="s">
-        <v>86</v>
+      <c r="B6" s="35" t="s">
+        <v>89</v>
+      </c>
+      <c r="C6" s="36" t="s">
+        <v>89</v>
+      </c>
+      <c r="D6" s="36" t="s">
+        <v>89</v>
+      </c>
+      <c r="E6" s="36" t="s">
+        <v>89</v>
+      </c>
+      <c r="F6" s="36" t="s">
+        <v>89</v>
+      </c>
+      <c r="G6" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="H6" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="I6" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="J6" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="K6" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="L6" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="M6" s="38" t="s">
+        <v>90</v>
+      </c>
+      <c r="N6" s="38" t="s">
+        <v>90</v>
+      </c>
+      <c r="O6" s="38" t="s">
+        <v>90</v>
+      </c>
+      <c r="P6" s="38" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q6" s="38" t="s">
+        <v>90</v>
+      </c>
+      <c r="R6" s="38" t="s">
+        <v>90</v>
+      </c>
+      <c r="S6" s="38" t="s">
+        <v>90</v>
+      </c>
+      <c r="T6" s="38" t="s">
+        <v>90</v>
+      </c>
+      <c r="U6" s="38" t="s">
+        <v>90</v>
+      </c>
+      <c r="V6" s="38" t="s">
+        <v>91</v>
+      </c>
+      <c r="W6" s="38" t="s">
+        <v>90</v>
+      </c>
+      <c r="X6" s="38" t="s">
+        <v>90</v>
+      </c>
+      <c r="Y6" s="38" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z6" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="AA6" s="38" t="s">
+        <v>90</v>
+      </c>
+      <c r="AB6" s="38" t="s">
+        <v>90</v>
+      </c>
+      <c r="AC6" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="AD6" s="38" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE6" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="AF6" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="AG6" s="38" t="s">
+        <v>90</v>
+      </c>
+      <c r="AH6" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="AI6" s="39" t="s">
+        <v>89</v>
       </c>
     </row>
-    <row r="7" spans="1:34" ht="91.5" customHeight="1">
-      <c r="A7" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="I7" s="9" t="s">
+    <row r="7" spans="1:35" ht="122.25" customHeight="1">
+      <c r="A7" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="J7" s="9" t="s">
+      <c r="B7" s="30" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" s="32" t="s">
         <v>93</v>
       </c>
-      <c r="K7" s="9" t="s">
+      <c r="H7" s="32" t="s">
         <v>94</v>
       </c>
-      <c r="L7" s="9" t="s">
+      <c r="I7" s="32" t="s">
         <v>95</v>
       </c>
-      <c r="M7" s="10" t="s">
+      <c r="J7" s="32" t="s">
         <v>96</v>
       </c>
-      <c r="N7" s="10" t="s">
+      <c r="K7" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="O7" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="P7" s="10" t="s">
+      <c r="L7" s="32" t="s">
         <v>98</v>
       </c>
-      <c r="Q7" s="10" t="s">
+      <c r="M7" s="33" t="s">
         <v>99</v>
       </c>
-      <c r="R7" s="10" t="s">
+      <c r="N7" s="33" t="s">
         <v>100</v>
       </c>
-      <c r="S7" s="10" t="s">
+      <c r="O7" s="33" t="s">
+        <v>57</v>
+      </c>
+      <c r="P7" s="33" t="s">
         <v>101</v>
       </c>
-      <c r="T7" s="10" t="s">
+      <c r="Q7" s="33" t="s">
         <v>102</v>
       </c>
-      <c r="U7" s="10" t="s">
+      <c r="R7" s="33" t="s">
         <v>103</v>
       </c>
-      <c r="V7" s="10" t="s">
+      <c r="S7" s="33" t="s">
         <v>104</v>
       </c>
-      <c r="W7" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="X7" s="10" t="s">
+      <c r="T7" s="33" t="s">
         <v>105</v>
       </c>
-      <c r="Y7" s="10" t="s">
+      <c r="U7" s="33" t="s">
         <v>106</v>
       </c>
-      <c r="Z7" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA7" s="10" t="s">
+      <c r="V7" s="33" t="s">
         <v>107</v>
       </c>
-      <c r="AB7" s="10" t="s">
+      <c r="W7" s="33" t="s">
+        <v>65</v>
+      </c>
+      <c r="X7" s="33" t="s">
         <v>108</v>
       </c>
-      <c r="AC7" s="10" t="s">
+      <c r="Y7" s="33" t="s">
         <v>109</v>
       </c>
-      <c r="AD7" s="10" t="s">
+      <c r="Z7" s="33" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA7" s="33" t="s">
         <v>110</v>
       </c>
-      <c r="AE7" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="AF7" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG7" s="10" t="s">
+      <c r="AB7" s="33" t="s">
         <v>111</v>
       </c>
-      <c r="AH7" s="10" t="s">
-        <v>41</v>
+      <c r="AC7" s="33" t="s">
+        <v>112</v>
+      </c>
+      <c r="AD7" s="33" t="s">
+        <v>113</v>
+      </c>
+      <c r="AE7" s="33" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF7" s="33" t="s">
+        <v>42</v>
+      </c>
+      <c r="AG7" s="33" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH7" s="33" t="s">
+        <v>42</v>
+      </c>
+      <c r="AI7" s="34" t="s">
+        <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:34" ht="91.5" customHeight="1">
-      <c r="A8" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="I8" s="9" t="s">
+    <row r="8" spans="1:35" ht="122.25" customHeight="1">
+      <c r="A8" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="J8" s="9" t="s">
+      <c r="B8" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="K8" s="9" t="s">
+      <c r="H8" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="L8" s="9" t="s">
+      <c r="I8" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="M8" s="10" t="s">
+      <c r="J8" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="N8" s="10" t="s">
+      <c r="K8" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="O8" s="10" t="s">
+      <c r="L8" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="P8" s="10" t="s">
+      <c r="M8" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="Q8" s="10" t="s">
+      <c r="N8" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="R8" s="10" t="s">
+      <c r="O8" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="S8" s="10" t="s">
+      <c r="P8" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="T8" s="10" t="s">
+      <c r="Q8" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="U8" s="10" t="s">
+      <c r="R8" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="V8" s="10" t="s">
+      <c r="S8" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="W8" s="10" t="s">
+      <c r="T8" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="X8" s="10" t="s">
+      <c r="U8" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="Y8" s="10" t="s">
+      <c r="V8" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="Z8" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA8" s="10" t="s">
+      <c r="W8" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="AB8" s="10" t="s">
+      <c r="X8" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="AC8" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="AD8" s="10" t="s">
+      <c r="Y8" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="AE8" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="AF8" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG8" s="10" t="s">
+      <c r="Z8" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA8" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="AH8" s="10" t="s">
-        <v>41</v>
+      <c r="AB8" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="AC8" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="AD8" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="AE8" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF8" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="AG8" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="AH8" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="AI8" s="9" t="s">
+        <v>42</v>
       </c>
     </row>
-    <row r="9" spans="1:34" ht="91.5" customHeight="1">
-      <c r="A9" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="D9" s="8" t="s">
+    <row r="9" spans="1:35" ht="122.25" customHeight="1">
+      <c r="A9" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="B9" s="20" t="s">
         <v>140</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="C9" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="G9" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="J9" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="K9" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="L9" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="M9" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="N9" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="O9" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="P9" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q9" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="R9" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="S9" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="T9" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="U9" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="V9" s="10" t="s">
+      <c r="D9" s="21" t="s">
         <v>142</v>
       </c>
-      <c r="W9" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="X9" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y9" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="Z9" s="10" t="s">
+      <c r="E9" s="21" t="s">
         <v>143</v>
       </c>
-      <c r="AA9" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB9" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="AC9" s="10" t="s">
+      <c r="F9" s="21" t="s">
         <v>144</v>
       </c>
-      <c r="AD9" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="AE9" s="10" t="s">
+      <c r="G9" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="H9" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="I9" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="J9" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="K9" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="L9" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="M9" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="N9" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="O9" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="P9" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q9" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="R9" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="S9" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="T9" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="U9" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="V9" s="23" t="s">
         <v>145</v>
       </c>
-      <c r="AF9" s="10" t="s">
+      <c r="W9" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="X9" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y9" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z9" s="23" t="s">
         <v>146</v>
       </c>
-      <c r="AG9" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH9" s="10" t="s">
+      <c r="AA9" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB9" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC9" s="23" t="s">
         <v>147</v>
       </c>
+      <c r="AD9" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE9" s="23" t="s">
+        <v>148</v>
+      </c>
+      <c r="AF9" s="23" t="s">
+        <v>149</v>
+      </c>
+      <c r="AG9" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH9" s="23" t="s">
+        <v>150</v>
+      </c>
+      <c r="AI9" s="24" t="s">
+        <v>151</v>
+      </c>
     </row>
-    <row r="10" spans="1:34" ht="30" customHeight="1">
-      <c r="A10" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="F10" s="8" t="s">
+    <row r="10" spans="1:35" ht="30" customHeight="1">
+      <c r="A10" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="G10" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="J10" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="K10" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="L10" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="M10" s="10" t="s">
-        <v>151</v>
-      </c>
-      <c r="N10" s="10" t="s">
-        <v>151</v>
-      </c>
-      <c r="O10" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="P10" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="Q10" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="R10" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="S10" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="T10" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="U10" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="V10" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="W10" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="X10" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="Y10" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="Z10" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="AA10" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="AB10" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="AC10" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="AD10" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="AE10" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="AF10" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="AG10" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="AH10" s="10" t="s">
-        <v>152</v>
+      <c r="B10" s="40" t="s">
+        <v>153</v>
+      </c>
+      <c r="C10" s="41" t="s">
+        <v>154</v>
+      </c>
+      <c r="D10" s="41" t="s">
+        <v>153</v>
+      </c>
+      <c r="E10" s="41" t="s">
+        <v>155</v>
+      </c>
+      <c r="F10" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="G10" s="42" t="s">
+        <v>156</v>
+      </c>
+      <c r="H10" s="42" t="s">
+        <v>155</v>
+      </c>
+      <c r="I10" s="42" t="s">
+        <v>155</v>
+      </c>
+      <c r="J10" s="42" t="s">
+        <v>156</v>
+      </c>
+      <c r="K10" s="42" t="s">
+        <v>156</v>
+      </c>
+      <c r="L10" s="42" t="s">
+        <v>153</v>
+      </c>
+      <c r="M10" s="43" t="s">
+        <v>155</v>
+      </c>
+      <c r="N10" s="43" t="s">
+        <v>155</v>
+      </c>
+      <c r="O10" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="P10" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q10" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="R10" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="S10" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="T10" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="U10" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="V10" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="W10" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="X10" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y10" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="Z10" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="AA10" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="AB10" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="AC10" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="AD10" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="AE10" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="AF10" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="AG10" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="AH10" s="43" t="s">
+        <v>155</v>
+      </c>
+      <c r="AI10" s="44" t="s">
+        <v>156</v>
       </c>
     </row>
   </sheetData>

--- a/sepreim/config.xlsx
+++ b/sepreim/config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\COPREIM\SEPREIM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="256" documentId="13_ncr:1_{FBC06D43-FC39-47E4-9407-81C46EA59553}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{70E29EF8-059F-4A4E-9D26-E6B6FCC30D34}"/>
+  <xr:revisionPtr revIDLastSave="259" documentId="13_ncr:1_{FBC06D43-FC39-47E4-9407-81C46EA59553}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{696232BB-BB63-4717-A504-E2E87410A142}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="5355" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="158">
   <si>
     <t>id</t>
   </si>
@@ -111,6 +111,9 @@
   </si>
   <si>
     <t>sentido_lombada</t>
+  </si>
+  <si>
+    <t>reserva_cola</t>
   </si>
   <si>
     <t>encadernacao_capa_dura</t>
@@ -912,16 +915,16 @@
   </cellStyleXfs>
   <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1259,16 +1262,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC9DC384-A7A3-4CB6-B76F-D3A8F330DE38}">
-  <dimension ref="A1:AI10"/>
+  <dimension ref="A1:AJ10"/>
   <sheetFormatPr defaultColWidth="54.5703125" defaultRowHeight="30" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="15.7109375" style="3" customWidth="1"/>
-    <col min="2" max="31" width="54.5703125" style="2"/>
-    <col min="32" max="32" width="54.5703125" style="4"/>
-    <col min="33" max="16384" width="54.5703125" style="2"/>
+    <col min="2" max="32" width="54.5703125" style="2"/>
+    <col min="33" max="33" width="54.5703125" style="4"/>
+    <col min="34" max="16384" width="54.5703125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" s="1" customFormat="1" ht="30" customHeight="1">
+    <row r="1" spans="1:36" s="1" customFormat="1" ht="30" customHeight="1">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -1371,299 +1374,308 @@
       <c r="AH1" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="19" t="s">
+      <c r="AI1" s="18" t="s">
         <v>34</v>
       </c>
+      <c r="AJ1" s="19" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="2" spans="1:35" ht="30" customHeight="1">
+    <row r="2" spans="1:36" ht="30" customHeight="1">
       <c r="A2" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B2" s="25" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C2" s="26" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D2" s="26" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E2" s="26" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F2" s="26" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G2" s="27" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H2" s="27" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I2" s="27" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J2" s="27" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K2" s="27" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L2" s="27" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M2" s="28" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N2" s="28" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O2" s="28" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="P2" s="28" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Q2" s="28" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="R2" s="28" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="S2" s="28" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="T2" s="28" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="U2" s="28" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="V2" s="28" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="W2" s="28" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="X2" s="28" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Y2" s="28" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Z2" s="28" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AA2" s="28" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AB2" s="28" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AC2" s="28" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AD2" s="28" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AE2" s="28" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AF2" s="28" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AG2" s="28" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AH2" s="28" t="s">
-        <v>39</v>
-      </c>
-      <c r="AI2" s="29" t="s">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="AI2" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="AJ2" s="29" t="s">
+        <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:35" ht="30" customHeight="1">
+    <row r="3" spans="1:36" ht="30" customHeight="1">
       <c r="A3" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B3" s="35" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C3" s="36" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D3" s="36" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E3" s="36" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F3" s="36" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G3" s="37" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H3" s="37" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I3" s="37" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J3" s="37" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K3" s="37" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L3" s="37" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M3" s="38" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N3" s="38" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O3" s="38" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="P3" s="38" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q3" s="38" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="R3" s="38" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="S3" s="38" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="T3" s="38" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="U3" s="38" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="V3" s="38" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="W3" s="38" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="X3" s="38" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Y3" s="38" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Z3" s="38" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AA3" s="38" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AB3" s="38" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AC3" s="38" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AD3" s="38" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AE3" s="38" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AF3" s="38" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AG3" s="38" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AH3" s="38" t="s">
         <v>42</v>
       </c>
-      <c r="AI3" s="39" t="s">
-        <v>41</v>
+      <c r="AI3" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="AJ3" s="39" t="s">
+        <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:35" ht="122.25" customHeight="1">
+    <row r="4" spans="1:36" ht="122.25" customHeight="1">
       <c r="A4" s="11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B4" s="30" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C4" s="31" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D4" s="31" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F4" s="31" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G4" s="32" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H4" s="32" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I4" s="32" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J4" s="32" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K4" s="32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L4" s="32" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M4" s="33" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="N4" s="33" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="O4" s="33" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="P4" s="33" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Q4" s="33" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R4" s="33" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S4" s="33" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="T4" s="33" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="U4" s="33" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V4" s="33" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="W4" s="33" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="X4" s="33" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Y4" s="33" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Z4" s="33" t="s">
         <v>68</v>
@@ -1692,88 +1704,91 @@
       <c r="AH4" s="33" t="s">
         <v>76</v>
       </c>
-      <c r="AI4" s="34" t="s">
+      <c r="AI4" s="33" t="s">
         <v>77</v>
       </c>
+      <c r="AJ4" s="34" t="s">
+        <v>78</v>
+      </c>
     </row>
-    <row r="5" spans="1:35" ht="122.25" customHeight="1">
+    <row r="5" spans="1:36" ht="122.25" customHeight="1">
       <c r="A5" s="11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N5" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O5" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P5" s="7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="Q5" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="R5" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S5" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="T5" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="U5" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="V5" s="7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="W5" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="X5" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Y5" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Z5" s="7" t="s">
-        <v>83</v>
+        <v>43</v>
       </c>
       <c r="AA5" s="7" t="s">
         <v>84</v>
@@ -1785,212 +1800,218 @@
         <v>86</v>
       </c>
       <c r="AD5" s="7" t="s">
-        <v>42</v>
+        <v>87</v>
       </c>
       <c r="AE5" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AF5" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AG5" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AH5" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="AI5" s="9" t="s">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="AI5" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="AJ5" s="9" t="s">
+        <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:35" ht="30.75" customHeight="1">
+    <row r="6" spans="1:36" ht="30.75" customHeight="1">
       <c r="A6" s="12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B6" s="35" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C6" s="36" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D6" s="36" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E6" s="36" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F6" s="36" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G6" s="37" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H6" s="37" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I6" s="37" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J6" s="37" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K6" s="37" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L6" s="37" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M6" s="38" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N6" s="38" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O6" s="38" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="P6" s="38" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Q6" s="38" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="R6" s="38" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="S6" s="38" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="T6" s="38" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="U6" s="38" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="V6" s="38" t="s">
+        <v>92</v>
+      </c>
+      <c r="W6" s="38" t="s">
         <v>91</v>
       </c>
-      <c r="W6" s="38" t="s">
-        <v>90</v>
-      </c>
       <c r="X6" s="38" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Y6" s="38" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Z6" s="38" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AA6" s="38" t="s">
         <v>90</v>
       </c>
       <c r="AB6" s="38" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AC6" s="38" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AD6" s="38" t="s">
         <v>90</v>
       </c>
       <c r="AE6" s="38" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AF6" s="38" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AG6" s="38" t="s">
         <v>90</v>
       </c>
       <c r="AH6" s="38" t="s">
-        <v>89</v>
-      </c>
-      <c r="AI6" s="39" t="s">
-        <v>89</v>
+        <v>91</v>
+      </c>
+      <c r="AI6" s="38" t="s">
+        <v>90</v>
+      </c>
+      <c r="AJ6" s="39" t="s">
+        <v>90</v>
       </c>
     </row>
-    <row r="7" spans="1:35" ht="122.25" customHeight="1">
+    <row r="7" spans="1:36" ht="122.25" customHeight="1">
       <c r="A7" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D7" s="31" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E7" s="31" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F7" s="31" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G7" s="32" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H7" s="32" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I7" s="32" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J7" s="32" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K7" s="32" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L7" s="32" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M7" s="33" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N7" s="33" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="O7" s="33" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="P7" s="33" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Q7" s="33" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="R7" s="33" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="S7" s="33" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T7" s="33" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="U7" s="33" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="V7" s="33" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="W7" s="33" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="X7" s="33" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Y7" s="33" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Z7" s="33" t="s">
-        <v>42</v>
+        <v>110</v>
       </c>
       <c r="AA7" s="33" t="s">
-        <v>110</v>
+        <v>43</v>
       </c>
       <c r="AB7" s="33" t="s">
         <v>111</v>
@@ -2002,340 +2023,352 @@
         <v>113</v>
       </c>
       <c r="AE7" s="33" t="s">
-        <v>42</v>
+        <v>114</v>
       </c>
       <c r="AF7" s="33" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AG7" s="33" t="s">
-        <v>114</v>
+        <v>43</v>
       </c>
       <c r="AH7" s="33" t="s">
-        <v>42</v>
-      </c>
-      <c r="AI7" s="34" t="s">
-        <v>42</v>
+        <v>115</v>
+      </c>
+      <c r="AI7" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="AJ7" s="34" t="s">
+        <v>43</v>
       </c>
     </row>
-    <row r="8" spans="1:35" ht="122.25" customHeight="1">
+    <row r="8" spans="1:36" ht="122.25" customHeight="1">
       <c r="A8" s="13" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N8" s="7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="O8" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="P8" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q8" s="7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="R8" s="7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="S8" s="7" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="T8" s="7" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="U8" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="V8" s="7" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="W8" s="7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="X8" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Y8" s="7" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Z8" s="7" t="s">
-        <v>42</v>
+        <v>135</v>
       </c>
       <c r="AA8" s="7" t="s">
-        <v>135</v>
+        <v>43</v>
       </c>
       <c r="AB8" s="7" t="s">
         <v>136</v>
       </c>
       <c r="AC8" s="7" t="s">
-        <v>42</v>
+        <v>137</v>
       </c>
       <c r="AD8" s="7" t="s">
-        <v>137</v>
+        <v>43</v>
       </c>
       <c r="AE8" s="7" t="s">
-        <v>42</v>
+        <v>138</v>
       </c>
       <c r="AF8" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AG8" s="7" t="s">
-        <v>138</v>
+        <v>43</v>
       </c>
       <c r="AH8" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="AI8" s="9" t="s">
-        <v>42</v>
+        <v>139</v>
+      </c>
+      <c r="AI8" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AJ8" s="9" t="s">
+        <v>43</v>
       </c>
     </row>
-    <row r="9" spans="1:35" ht="122.25" customHeight="1">
+    <row r="9" spans="1:36" ht="122.25" customHeight="1">
       <c r="A9" s="14" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E9" s="21" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F9" s="21" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G9" s="22" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H9" s="22" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I9" s="22" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J9" s="22" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K9" s="22" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L9" s="22" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M9" s="23" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N9" s="23" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O9" s="23" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P9" s="23" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q9" s="23" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="R9" s="23" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="S9" s="23" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="T9" s="23" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="U9" s="23" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="V9" s="23" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="W9" s="23" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="X9" s="23" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Y9" s="23" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Z9" s="23" t="s">
-        <v>146</v>
+        <v>43</v>
       </c>
       <c r="AA9" s="23" t="s">
-        <v>42</v>
+        <v>147</v>
       </c>
       <c r="AB9" s="23" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AC9" s="23" t="s">
-        <v>147</v>
+        <v>43</v>
       </c>
       <c r="AD9" s="23" t="s">
-        <v>42</v>
+        <v>148</v>
       </c>
       <c r="AE9" s="23" t="s">
-        <v>148</v>
+        <v>43</v>
       </c>
       <c r="AF9" s="23" t="s">
         <v>149</v>
       </c>
       <c r="AG9" s="23" t="s">
-        <v>42</v>
+        <v>150</v>
       </c>
       <c r="AH9" s="23" t="s">
-        <v>150</v>
-      </c>
-      <c r="AI9" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="AI9" s="23" t="s">
         <v>151</v>
       </c>
+      <c r="AJ9" s="24" t="s">
+        <v>152</v>
+      </c>
     </row>
-    <row r="10" spans="1:35" ht="30" customHeight="1">
+    <row r="10" spans="1:36" ht="30" customHeight="1">
       <c r="A10" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B10" s="40" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C10" s="41" t="s">
+        <v>155</v>
+      </c>
+      <c r="D10" s="41" t="s">
         <v>154</v>
       </c>
-      <c r="D10" s="41" t="s">
-        <v>153</v>
-      </c>
       <c r="E10" s="41" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F10" s="41" t="s">
+        <v>157</v>
+      </c>
+      <c r="G10" s="42" t="s">
+        <v>157</v>
+      </c>
+      <c r="H10" s="42" t="s">
         <v>156</v>
       </c>
-      <c r="G10" s="42" t="s">
+      <c r="I10" s="42" t="s">
         <v>156</v>
       </c>
-      <c r="H10" s="42" t="s">
-        <v>155</v>
-      </c>
-      <c r="I10" s="42" t="s">
-        <v>155</v>
-      </c>
       <c r="J10" s="42" t="s">
+        <v>157</v>
+      </c>
+      <c r="K10" s="42" t="s">
+        <v>157</v>
+      </c>
+      <c r="L10" s="42" t="s">
+        <v>154</v>
+      </c>
+      <c r="M10" s="43" t="s">
         <v>156</v>
       </c>
-      <c r="K10" s="42" t="s">
+      <c r="N10" s="43" t="s">
         <v>156</v>
       </c>
-      <c r="L10" s="42" t="s">
-        <v>153</v>
-      </c>
-      <c r="M10" s="43" t="s">
-        <v>155</v>
-      </c>
-      <c r="N10" s="43" t="s">
-        <v>155</v>
-      </c>
       <c r="O10" s="43" t="s">
+        <v>157</v>
+      </c>
+      <c r="P10" s="43" t="s">
+        <v>157</v>
+      </c>
+      <c r="Q10" s="43" t="s">
+        <v>157</v>
+      </c>
+      <c r="R10" s="43" t="s">
+        <v>157</v>
+      </c>
+      <c r="S10" s="43" t="s">
+        <v>157</v>
+      </c>
+      <c r="T10" s="43" t="s">
+        <v>157</v>
+      </c>
+      <c r="U10" s="43" t="s">
+        <v>157</v>
+      </c>
+      <c r="V10" s="43" t="s">
+        <v>157</v>
+      </c>
+      <c r="W10" s="43" t="s">
+        <v>157</v>
+      </c>
+      <c r="X10" s="43" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y10" s="43" t="s">
+        <v>157</v>
+      </c>
+      <c r="Z10" s="43" t="s">
+        <v>157</v>
+      </c>
+      <c r="AA10" s="43" t="s">
+        <v>157</v>
+      </c>
+      <c r="AB10" s="43" t="s">
+        <v>157</v>
+      </c>
+      <c r="AC10" s="43" t="s">
+        <v>157</v>
+      </c>
+      <c r="AD10" s="43" t="s">
+        <v>157</v>
+      </c>
+      <c r="AE10" s="43" t="s">
+        <v>157</v>
+      </c>
+      <c r="AF10" s="43" t="s">
+        <v>157</v>
+      </c>
+      <c r="AG10" s="43" t="s">
+        <v>157</v>
+      </c>
+      <c r="AH10" s="43" t="s">
+        <v>157</v>
+      </c>
+      <c r="AI10" s="43" t="s">
         <v>156</v>
       </c>
-      <c r="P10" s="43" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q10" s="43" t="s">
-        <v>156</v>
-      </c>
-      <c r="R10" s="43" t="s">
-        <v>156</v>
-      </c>
-      <c r="S10" s="43" t="s">
-        <v>156</v>
-      </c>
-      <c r="T10" s="43" t="s">
-        <v>156</v>
-      </c>
-      <c r="U10" s="43" t="s">
-        <v>156</v>
-      </c>
-      <c r="V10" s="43" t="s">
-        <v>156</v>
-      </c>
-      <c r="W10" s="43" t="s">
-        <v>156</v>
-      </c>
-      <c r="X10" s="43" t="s">
-        <v>156</v>
-      </c>
-      <c r="Y10" s="43" t="s">
-        <v>156</v>
-      </c>
-      <c r="Z10" s="43" t="s">
-        <v>156</v>
-      </c>
-      <c r="AA10" s="43" t="s">
-        <v>156</v>
-      </c>
-      <c r="AB10" s="43" t="s">
-        <v>156</v>
-      </c>
-      <c r="AC10" s="43" t="s">
-        <v>156</v>
-      </c>
-      <c r="AD10" s="43" t="s">
-        <v>156</v>
-      </c>
-      <c r="AE10" s="43" t="s">
-        <v>156</v>
-      </c>
-      <c r="AF10" s="43" t="s">
-        <v>156</v>
-      </c>
-      <c r="AG10" s="43" t="s">
-        <v>156</v>
-      </c>
-      <c r="AH10" s="43" t="s">
-        <v>155</v>
-      </c>
-      <c r="AI10" s="44" t="s">
-        <v>156</v>
+      <c r="AJ10" s="44" t="s">
+        <v>157</v>
       </c>
     </row>
   </sheetData>

--- a/sepreim/config.xlsx
+++ b/sepreim/config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\COPREIM\SEPREIM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="259" documentId="13_ncr:1_{FBC06D43-FC39-47E4-9407-81C46EA59553}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{696232BB-BB63-4717-A504-E2E87410A142}"/>
+  <xr:revisionPtr revIDLastSave="263" documentId="13_ncr:1_{FBC06D43-FC39-47E4-9407-81C46EA59553}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9CCC54EA-0B9D-4C30-BAF6-2596D7C7DB8C}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="5355" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="161">
   <si>
     <t>id</t>
   </si>
@@ -243,6 +243,9 @@
   </si>
   <si>
     <t>Sentido da lombada correto</t>
+  </si>
+  <si>
+    <t>Parte interna da lombada em branco</t>
   </si>
   <si>
     <t>Compatível com encadernação com capa dura</t>
@@ -375,6 +378,9 @@
     <t>Conteúdo da lombada em sentido invertido</t>
   </si>
   <si>
+    <t>Impressão na parte interna da lombada</t>
+  </si>
+  <si>
     <t>Quantidade de páginas é pequena para acabamento com cola</t>
   </si>
   <si>
@@ -448,6 +454,9 @@
   </si>
   <si>
     <t>Girar 180 graus, de forma que a leitura do texto fique de cima para baixo; ou autorizar a impressão desta forma.</t>
+  </si>
+  <si>
+    <t>Deixar a parte interna da lombada em branco, porque a tinta nessa área prejudica a colagem do miolo.</t>
   </si>
   <si>
     <t>Alterar capa para grampo (sem lombada).</t>
@@ -1678,48 +1687,48 @@
         <v>68</v>
       </c>
       <c r="Z4" s="33" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AA4" s="33" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AB4" s="33" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AC4" s="33" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD4" s="33" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AE4" s="33" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AF4" s="33" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AG4" s="33" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH4" s="33" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AI4" s="33" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AJ4" s="34" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:36" ht="122.25" customHeight="1">
       <c r="A5" s="11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>43</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>43</v>
@@ -1758,13 +1767,13 @@
         <v>43</v>
       </c>
       <c r="P5" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q5" s="7" t="s">
         <v>43</v>
       </c>
       <c r="R5" s="7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="S5" s="7" t="s">
         <v>43</v>
@@ -1776,7 +1785,7 @@
         <v>43</v>
       </c>
       <c r="V5" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="W5" s="7" t="s">
         <v>43</v>
@@ -1791,16 +1800,16 @@
         <v>43</v>
       </c>
       <c r="AA5" s="7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB5" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AC5" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AD5" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AE5" s="7" t="s">
         <v>43</v>
@@ -1815,7 +1824,7 @@
         <v>43</v>
       </c>
       <c r="AI5" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AJ5" s="9" t="s">
         <v>43</v>
@@ -1823,117 +1832,117 @@
     </row>
     <row r="6" spans="1:36" ht="30.75" customHeight="1">
       <c r="A6" s="12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B6" s="35" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C6" s="36" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D6" s="36" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E6" s="36" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F6" s="36" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G6" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="H6" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="I6" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="J6" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="K6" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="L6" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="M6" s="38" t="s">
+        <v>92</v>
+      </c>
+      <c r="N6" s="38" t="s">
+        <v>92</v>
+      </c>
+      <c r="O6" s="38" t="s">
+        <v>92</v>
+      </c>
+      <c r="P6" s="38" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q6" s="38" t="s">
+        <v>92</v>
+      </c>
+      <c r="R6" s="38" t="s">
+        <v>92</v>
+      </c>
+      <c r="S6" s="38" t="s">
+        <v>92</v>
+      </c>
+      <c r="T6" s="38" t="s">
+        <v>92</v>
+      </c>
+      <c r="U6" s="38" t="s">
+        <v>92</v>
+      </c>
+      <c r="V6" s="38" t="s">
+        <v>93</v>
+      </c>
+      <c r="W6" s="38" t="s">
+        <v>92</v>
+      </c>
+      <c r="X6" s="38" t="s">
+        <v>92</v>
+      </c>
+      <c r="Y6" s="38" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z6" s="38" t="s">
+        <v>92</v>
+      </c>
+      <c r="AA6" s="38" t="s">
         <v>91</v>
       </c>
-      <c r="H6" s="37" t="s">
+      <c r="AB6" s="38" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC6" s="38" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD6" s="38" t="s">
         <v>91</v>
       </c>
-      <c r="I6" s="37" t="s">
+      <c r="AE6" s="38" t="s">
+        <v>92</v>
+      </c>
+      <c r="AF6" s="38" t="s">
         <v>91</v>
       </c>
-      <c r="J6" s="37" t="s">
+      <c r="AG6" s="38" t="s">
         <v>91</v>
       </c>
-      <c r="K6" s="37" t="s">
+      <c r="AH6" s="38" t="s">
+        <v>92</v>
+      </c>
+      <c r="AI6" s="38" t="s">
         <v>91</v>
       </c>
-      <c r="L6" s="37" t="s">
+      <c r="AJ6" s="39" t="s">
         <v>91</v>
-      </c>
-      <c r="M6" s="38" t="s">
-        <v>91</v>
-      </c>
-      <c r="N6" s="38" t="s">
-        <v>91</v>
-      </c>
-      <c r="O6" s="38" t="s">
-        <v>91</v>
-      </c>
-      <c r="P6" s="38" t="s">
-        <v>91</v>
-      </c>
-      <c r="Q6" s="38" t="s">
-        <v>91</v>
-      </c>
-      <c r="R6" s="38" t="s">
-        <v>91</v>
-      </c>
-      <c r="S6" s="38" t="s">
-        <v>91</v>
-      </c>
-      <c r="T6" s="38" t="s">
-        <v>91</v>
-      </c>
-      <c r="U6" s="38" t="s">
-        <v>91</v>
-      </c>
-      <c r="V6" s="38" t="s">
-        <v>92</v>
-      </c>
-      <c r="W6" s="38" t="s">
-        <v>91</v>
-      </c>
-      <c r="X6" s="38" t="s">
-        <v>91</v>
-      </c>
-      <c r="Y6" s="38" t="s">
-        <v>91</v>
-      </c>
-      <c r="Z6" s="38" t="s">
-        <v>91</v>
-      </c>
-      <c r="AA6" s="38" t="s">
-        <v>90</v>
-      </c>
-      <c r="AB6" s="38" t="s">
-        <v>91</v>
-      </c>
-      <c r="AC6" s="38" t="s">
-        <v>91</v>
-      </c>
-      <c r="AD6" s="38" t="s">
-        <v>90</v>
-      </c>
-      <c r="AE6" s="38" t="s">
-        <v>91</v>
-      </c>
-      <c r="AF6" s="38" t="s">
-        <v>90</v>
-      </c>
-      <c r="AG6" s="38" t="s">
-        <v>90</v>
-      </c>
-      <c r="AH6" s="38" t="s">
-        <v>91</v>
-      </c>
-      <c r="AI6" s="38" t="s">
-        <v>90</v>
-      </c>
-      <c r="AJ6" s="39" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:36" ht="122.25" customHeight="1">
       <c r="A7" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B7" s="30" t="s">
         <v>43</v>
@@ -1951,79 +1960,79 @@
         <v>43</v>
       </c>
       <c r="G7" s="32" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H7" s="32" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I7" s="32" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J7" s="32" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K7" s="32" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L7" s="32" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M7" s="33" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N7" s="33" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O7" s="33" t="s">
         <v>58</v>
       </c>
       <c r="P7" s="33" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="Q7" s="33" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="R7" s="33" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="S7" s="33" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T7" s="33" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="U7" s="33" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="V7" s="33" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="W7" s="33" t="s">
         <v>66</v>
       </c>
       <c r="X7" s="33" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Y7" s="33" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Z7" s="33" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="AA7" s="33" t="s">
         <v>43</v>
       </c>
       <c r="AB7" s="33" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="AC7" s="33" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AD7" s="33" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AE7" s="33" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="AF7" s="33" t="s">
         <v>43</v>
@@ -2032,7 +2041,7 @@
         <v>43</v>
       </c>
       <c r="AH7" s="33" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="AI7" s="33" t="s">
         <v>43</v>
@@ -2043,7 +2052,7 @@
     </row>
     <row r="8" spans="1:36" ht="122.25" customHeight="1">
       <c r="A8" s="13" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B8" s="8" t="s">
         <v>43</v>
@@ -2061,79 +2070,79 @@
         <v>43</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="N8" s="7" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="O8" s="7" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="P8" s="7" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="Q8" s="7" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="R8" s="7" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="S8" s="7" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="T8" s="7" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="U8" s="7" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="V8" s="7" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="W8" s="7" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="X8" s="7" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="Y8" s="7" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="Z8" s="7" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="AA8" s="7" t="s">
         <v>43</v>
       </c>
       <c r="AB8" s="7" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="AC8" s="7" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="AD8" s="7" t="s">
         <v>43</v>
       </c>
       <c r="AE8" s="7" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="AF8" s="7" t="s">
         <v>43</v>
@@ -2142,7 +2151,7 @@
         <v>43</v>
       </c>
       <c r="AH8" s="7" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="AI8" s="7" t="s">
         <v>43</v>
@@ -2153,22 +2162,22 @@
     </row>
     <row r="9" spans="1:36" ht="122.25" customHeight="1">
       <c r="A9" s="14" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E9" s="21" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="F9" s="21" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="G9" s="22" t="s">
         <v>43</v>
@@ -2216,7 +2225,7 @@
         <v>43</v>
       </c>
       <c r="V9" s="23" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="W9" s="23" t="s">
         <v>43</v>
@@ -2231,7 +2240,7 @@
         <v>43</v>
       </c>
       <c r="AA9" s="23" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="AB9" s="23" t="s">
         <v>43</v>
@@ -2240,135 +2249,135 @@
         <v>43</v>
       </c>
       <c r="AD9" s="23" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="AE9" s="23" t="s">
         <v>43</v>
       </c>
       <c r="AF9" s="23" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AG9" s="23" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="AH9" s="23" t="s">
         <v>43</v>
       </c>
       <c r="AI9" s="23" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="AJ9" s="24" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="10" spans="1:36" ht="30" customHeight="1">
       <c r="A10" s="13" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B10" s="40" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C10" s="41" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D10" s="41" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E10" s="41" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="F10" s="41" t="s">
+        <v>160</v>
+      </c>
+      <c r="G10" s="42" t="s">
+        <v>160</v>
+      </c>
+      <c r="H10" s="42" t="s">
+        <v>159</v>
+      </c>
+      <c r="I10" s="42" t="s">
+        <v>159</v>
+      </c>
+      <c r="J10" s="42" t="s">
+        <v>160</v>
+      </c>
+      <c r="K10" s="42" t="s">
+        <v>160</v>
+      </c>
+      <c r="L10" s="42" t="s">
         <v>157</v>
       </c>
-      <c r="G10" s="42" t="s">
-        <v>157</v>
-      </c>
-      <c r="H10" s="42" t="s">
-        <v>156</v>
-      </c>
-      <c r="I10" s="42" t="s">
-        <v>156</v>
-      </c>
-      <c r="J10" s="42" t="s">
-        <v>157</v>
-      </c>
-      <c r="K10" s="42" t="s">
-        <v>157</v>
-      </c>
-      <c r="L10" s="42" t="s">
-        <v>154</v>
-      </c>
       <c r="M10" s="43" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="N10" s="43" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="O10" s="43" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="P10" s="43" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="Q10" s="43" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="R10" s="43" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="S10" s="43" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="T10" s="43" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="U10" s="43" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="V10" s="43" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="W10" s="43" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="X10" s="43" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="Y10" s="43" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="Z10" s="43" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="AA10" s="43" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="AB10" s="43" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="AC10" s="43" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="AD10" s="43" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="AE10" s="43" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="AF10" s="43" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="AG10" s="43" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="AH10" s="43" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="AI10" s="43" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="AJ10" s="44" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
   </sheetData>

--- a/sepreim/config.xlsx
+++ b/sepreim/config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\COPREIM\SEPREIM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="263" documentId="13_ncr:1_{FBC06D43-FC39-47E4-9407-81C46EA59553}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9CCC54EA-0B9D-4C30-BAF6-2596D7C7DB8C}"/>
+  <xr:revisionPtr revIDLastSave="264" documentId="13_ncr:1_{FBC06D43-FC39-47E4-9407-81C46EA59553}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6500FD5B-B139-4CBD-A474-1F09C0C7B57E}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="5355" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="162">
   <si>
     <t>id</t>
   </si>
@@ -523,6 +523,9 @@
   </si>
   <si>
     <t>impressao</t>
+  </si>
+  <si>
+    <t>expediente</t>
   </si>
 </sst>
 </file>
@@ -2371,7 +2374,7 @@
         <v>160</v>
       </c>
       <c r="AH10" s="43" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AI10" s="43" t="s">
         <v>159</v>
